--- a/reports/hazop_vision_system_13.xlsx
+++ b/reports/hazop_vision_system_13.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -68,7 +68,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Model reading: This P&amp;ID depicts a gas wellhead system, including chemical injection facilities for scale inhibitor, MEOH, and MEG. It illustrates the well flow path through various safety and control valves (e.g., SSSV, master valve, wing valve, choke valve) to a multiphase meter (13-XJ54) and ultimately to a production manifold. The diagram also shows connections to a wellhead control panel (13-JB61) and hydraulic power units.</t>
+          <t>Model reading: This P&amp;ID illustrates the flow from a gas wellhead (A4), showing the main production path, various chemical injection points (Scale Inhibitor, MEOH, MEG), and connections to a multiphase meter (13-XJ54) and ultimately a production manifold. It includes controls and safety devices for wellhead operation, such as choke valves and emergency shutdown valves.</t>
         </is>
       </c>
     </row>
@@ -520,17 +520,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>No measurement / Less measurement / More measurement</t>
+          <t>No flow / More flow</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The well production is routed through a single Multiphase Meter (13-XJ54) without an apparent bypass. Failure or maintenance of this meter would result in loss of production measurement or require well shutdown, representing a single point of failure for measurement.</t>
+          <t>All chemical injection lines (Scale Inhibitor, MEOH, MEG) converge into a single header upstream of valve XV 2271. Failure of this valve could block all injections, potentially impacting flow assurance or chemical treatment, or lead to uncontrolled injection if it fails open.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13-XJ54, FI 2275A, FI 2275B, FI 2275C, FE 2278, TIT 2273, DT 2276, PIT 2274, XI 2270, XE 2270, TI 2273</t>
+          <t>XV 2271, H042-P-*F-006, H042-P-*F-004, H042-P-*F-005</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Notes 18 and 30 specify pressure differential permissives across the wing valve and master valve, with a maximum of 30 bar for the master valve. Exceeding these differentials could indicate an issue with valve operation, blockage, or could lead to equipment damage or unsafe conditions during operation.</t>
+          <t>Note 30 specifies a maximum 30 bar differential pressure across the master valve (ESV 2252), implying a potential for high differential pressure that could damage the valve or upstream/downstream equipment if not controlled by instrumentation like PDI 2260.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PDI 2260, PI 2282, 13-ESV 2253, 13-ESV 2252, 13-PT 2262, 13-PT 2264B, 13-HY 2264A</t>
+          <t>ESV 2252, PDI 2260, PI 2256A, PI 2256B</t>
         </is>
       </c>
     </row>
@@ -560,17 +560,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Erosion / Leakage / Mechanical failure</t>
+          <t>Wrong position / More flow / No flow</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Notes 14 and 27 explicitly highlight potential for sand erosion, particularly in the mixing tee and downstream of the choke valve to the multiphase meter inlet. This indicates a risk of material degradation, leading to potential loss of containment or equipment failure if not regularly inspected and maintained.</t>
+          <t>The choke valve (HV 2264) is described as a "step type valve" that "will remain in the position it is set" upon failure (Note 16). This fixed failure mode means that a failure could result in uncontrolled flow (too much or too little) from the wellhead, impacting production or safety.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>SI 2805, SI 2902, SI 2804, SI 3001, 13-XJ54, 13-XV 2253</t>
+          <t>HV 2264</t>
         </is>
       </c>
     </row>
@@ -580,17 +580,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Uncontrolled flow / More flow / Less flow</t>
+          <t>Erosion / Leak</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Note 16 states that the choke valve (13-XV 2253) is a 'step type valve' and 'on failure the valve will remain in the position it is set'. This failure mode implies that the flow rate cannot be dynamically adjusted or shut down upon loss of control, potentially leading to undesired flow conditions (e.g., high or low flow) and process upsets.</t>
+          <t>Sand detection probes (XE 2270, NE 2269) are specified due to erosion concerns (Notes 11, 12, 15). This indicates a known risk of erosion, particularly downstream of the choke valve, which could lead to loss of containment if not adequately monitored and mitigated.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13-XV 2253, PSD</t>
+          <t>XE 2270, NE 2269</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Contamination / Incorrect purge / No purge</t>
+          <t>Inadequate isolation / Maintenance hazard</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The Nitrogen (N2) purge system (Note 22) connected to various points on the wellhead panel introduces a potential for incorrect purging, leading to process contamination if N2 enters the process stream, or inadequate purging leading to safety hazards if hazardous substances are not properly removed.</t>
+          <t>Notes 23 and 24 concerning the multiphase meter (13-XJ54) refer to "ISOLATION VALVES FOR FIT BY PIPING DEPARTMENT." This suggests potential uncertainty or reliance on future design for critical isolation, which could lead to inadequate isolation during maintenance or operational issues.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PX 2299, PDI 2299, 13-2015PT, 13-2075PT, 13-2076PT, 13-2077PT</t>
+          <t>13-XJ54, FE 2275, DT 2276, TIT 2273, FI 2275A, FI 2275B, FI 2275C, PI 2274</t>
         </is>
       </c>
     </row>
@@ -620,17 +620,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>No flow (injection) / Less flow (injection)</t>
+          <t>Hydraulic shock / Too fast operation</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Each chemical injection line (Scale Inhibitor, MEOH, MEG) appears to be a single, non-redundant path. A failure in any of these lines or their associated control valves (e.g., 13-XV 2271 for MEOH) could lead to complete loss or insufficient chemical treatment, potentially causing issues like hydrate formation, scaling, or corrosion in the well and downstream facilities.</t>
+          <t>The "QUICK DUMP VALVE" (XY 2253) is associated with Note 9, which warns about "VALVE OPENING TIME LONG ENOUGH TO AVOID HYDRAULIC SHOCK." This highlights a design consideration for potential hydraulic shock if the valve operates too rapidly, posing a risk to piping integrity.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>H042-P-XF-006, H042-P-XF-004, H042-P-XF-005, 13-XV 2271, 13-XV 2272</t>
+          <t>XY 2253</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -680,75 +680,75 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>13-XJ54</t>
+          <t>XV 2271</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>bekreftet i uttrekket</t>
+          <t>bekreftet ((type, nr)-match)</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+          <t>observation 1: No flow / More flow</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>FI 2275A</t>
+          <t>H042-P-*F-006</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>bekreftet ((type, nr)-match)</t>
+          <t>ukjent format / mulig hallusinasjon</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+          <t>observation 1: No flow / More flow</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>FI 2275B</t>
+          <t>H042-P-*F-004</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>bekreftet ((type, nr)-match)</t>
+          <t>ukjent format / mulig hallusinasjon</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+          <t>observation 1: No flow / More flow</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>FI 2275C</t>
+          <t>H042-P-*F-005</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>bekreftet ((type, nr)-match)</t>
+          <t>ukjent format / mulig hallusinasjon</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+          <t>observation 1: No flow / More flow</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>FE 2278</t>
+          <t>ESV 2252</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -758,65 +758,65 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+          <t>observation 2: High differential pressure</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>TIT 2273</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>PDI 2260</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>observation 2: High differential pressure</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>DT 2276</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>PI 2256A</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>observation 2: High differential pressure</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>PIT 2274</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>PI 2256B</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>observation 2: High differential pressure</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>XI 2270</t>
+          <t>HV 2264</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+          <t>observation 3: Wrong position / More flow / No flow</t>
         </is>
       </c>
     </row>
@@ -843,65 +843,65 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+          <t>observation 4: Erosion / Leak</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>TI 2273</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>observation 1: No measurement / Less measurement / More measurement</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>NE 2269</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>observation 4: Erosion / Leak</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>PDI 2260</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>observation 2: High differential pressure</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>13-XJ54</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>PI 2282</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>observation 2: High differential pressure</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>FE 2275</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>13-ESV 2253</t>
+          <t>DT 2276</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -911,14 +911,14 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>observation 2: High differential pressure</t>
+          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>13-ESV 2252</t>
+          <t>TIT 2273</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -928,150 +928,150 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>observation 2: High differential pressure</t>
+          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>13-PT 2262</t>
+          <t>FI 2275A</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>bekreftet i uttrekket</t>
+          <t>bekreftet ((type, nr)-match)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>observation 2: High differential pressure</t>
+          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>13-PT 2264B</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>FI 2275B</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>FI 2275C</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>PI 2274</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>XY 2253</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Hydraulic shock / Too fast operation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>XV 2271</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>XY 2253</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: quick dump valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>ESV 2252</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>NY KANDIDAT - sjekk tegning</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>observation 2: High differential pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>13-HY 2264A</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>observation 2: High differential pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>SI 2805</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>observation 3: Erosion / Leakage / Mechanical failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>SI 2902</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>observation 3: Erosion / Leakage / Mechanical failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>SI 2804</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>observation 3: Erosion / Leakage / Mechanical failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>SI 3001</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>observation 3: Erosion / Leakage / Mechanical failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>13-XJ54</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>observation 3: Erosion / Leakage / Mechanical failure</t>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: emergency shutoff valve</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>13-XV 2253</t>
+          <t>ESV 2253</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1081,14 +1081,14 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>observation 3: Erosion / Leakage / Mechanical failure</t>
+          <t>symbol-only candidate: emergency shutoff valve</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>13-XV 2253</t>
+          <t>HV 2264</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1098,558 +1098,48 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>observation 4: Uncontrolled flow / More flow / Less flow</t>
+          <t>symbol-only candidate: choke valve</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>PSD</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>ukjent format / mulig hallusinasjon</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>observation 4: Uncontrolled flow / More flow / Less flow</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>XY 2279</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: valve</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>PX 2299</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>observation 5: Contamination / Incorrect purge / No purge</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>PDI 2299</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>observation 5: Contamination / Incorrect purge / No purge</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>XV 2279</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: valve</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>13-2015PT</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>observation 5: Contamination / Incorrect purge / No purge</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>13-2075PT</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>observation 5: Contamination / Incorrect purge / No purge</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>13-2076PT</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>observation 5: Contamination / Incorrect purge / No purge</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>13-2077PT</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>observation 5: Contamination / Incorrect purge / No purge</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>H042-P-XF-006</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>ukjent format / mulig hallusinasjon</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>observation 6: No flow (injection) / Less flow (injection)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>H042-P-XF-004</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>ukjent format / mulig hallusinasjon</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>observation 6: No flow (injection) / Less flow (injection)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>H042-P-XF-005</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>ukjent format / mulig hallusinasjon</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>observation 6: No flow (injection) / Less flow (injection)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>13-XV 2271</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>observation 6: No flow (injection) / Less flow (injection)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>13-XV 2272</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>observation 6: No flow (injection) / Less flow (injection)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>13-XV 2271</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: globe valve with actuator (control valve)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>PSD</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>ukjent format / mulig hallusinasjon</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: safety interlock symbol</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>HIC 2264</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: hand indicator controller</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>ZI 2264</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: position indicator</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>ZS 2264L</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: position switch (low)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>HV 2287</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: hand valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>PI 2260A</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: pressure indicator</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>PDI 2260</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: pressure differential indicator</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>PX 2299</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: pressure transmitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>TI 2263</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: temperature indicator</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>TT 2263</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: temperature transmitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>ESV 2253</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: emergency shutoff valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>XY 2252</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: actuator</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>NE 2269</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: noise element / acoustic sensor</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>FE 2278</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: flow element (orifice plate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>DT 2276</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: density transmitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>TIT 2273</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: temperature indicator transmitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>PIT 2274</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: pressure indicator transmitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>SI 2805</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: sand indicator</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>SI 3001</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: sand indicator</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Totals: 7 verified · 13 verified (normalised) · 32 new candidates · 5 unknown format</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Totals: 1 verified · 13 verified (normalised) · 10 new candidates · 3 unknown format</t>
         </is>
       </c>
     </row>

--- a/reports/hazop_vision_system_13.xlsx
+++ b/reports/hazop_vision_system_13.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -68,7 +68,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Model reading: This P&amp;ID illustrates the flow from a gas wellhead (A4), showing the main production path, various chemical injection points (Scale Inhibitor, MEOH, MEG), and connections to a multiphase meter (13-XJ54) and ultimately a production manifold. It includes controls and safety devices for wellhead operation, such as choke valves and emergency shutdown valves.</t>
+          <t>Model reading: The drawing depicts a Gas Wellhead A4 system, showing the main wellhead tree, chemical injection facilities (Scale Inhibitor, MEOH, MEG), a multiphase flow meter with bypass, and various safety instrumentation. It details hydraulic power supply connections for valve actuation and also includes a slot allocation plan for production wells.</t>
         </is>
       </c>
     </row>
@@ -520,17 +520,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>No flow / More flow</t>
+          <t>No flow (of chemical), Less flow (of chemical), Maintenance difficulty</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>All chemical injection lines (Scale Inhibitor, MEOH, MEG) converge into a single header upstream of valve XV 2271. Failure of this valve could block all injections, potentially impacting flow assurance or chemical treatment, or lead to uncontrolled injection if it fails open.</t>
+          <t>Chemical injection lines for Scale Inhibitor, MEOH, and MEG appear to lack clearly tagged individual isolation valves before entering the main well stream, potentially hindering precise control or safe isolation during maintenance.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>XV 2271, H042-P-*F-006, H042-P-*F-004, H042-P-*F-005</t>
+          <t>H042-P-F-006, H042-P-F-004, H042-P-F-005, 42-2000CC, 42-2000CA, 42-2000CG</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>High differential pressure</t>
+          <t>More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Note 30 specifies a maximum 30 bar differential pressure across the master valve (ESV 2252), implying a potential for high differential pressure that could damage the valve or upstream/downstream equipment if not controlled by instrumentation like PDI 2260.</t>
+          <t>A bypass line around the multiphase meter (13-XJ54) is present. While useful for maintenance, it creates a potential for unmeasured flow if the bypass is inadvertently opened or leaks, impacting production accounting and process control.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ESV 2252, PDI 2260, PI 2256A, PI 2256B</t>
+          <t>13-XJ54, 13-PDI 2260, 13-PI 2277, 13-LL 2277, 13-PT 2277, 13-2015PT, 13-2075PT, 13-2077PT, 13-2076PT, 13-2126PT, NOTE 15</t>
         </is>
       </c>
     </row>
@@ -560,17 +560,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Wrong position / More flow / No flow</t>
+          <t>High pressure, Low pressure, No isolation</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The choke valve (HV 2264) is described as a "step type valve" that "will remain in the position it is set" upon failure (Note 16). This fixed failure mode means that a failure could result in uncontrolled flow (too much or too little) from the wellhead, impacting production or safety.</t>
+          <t>Multiple pressure indicators (PI 2260, PI 2256A, PI 2255A, PI 2254A) are present on the wellhead, some with associated Dublok valves (Note 31). The specific pressure isolation philosophy and required integrity level for each tap are not explicitly detailed, posing a potential risk if isolation fails or is compromised.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>HV 2264</t>
+          <t>13-PI 2260, 13-PI 2256A, 13-PI 2255A, 13-PI 2254A, 13-PI 2256B, 13-PI 2255B, 13-PI 2254B, NOTE 31</t>
         </is>
       </c>
     </row>
@@ -580,17 +580,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Erosion / Leak</t>
+          <t>No flow, More flow, Less control</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Sand detection probes (XE 2270, NE 2269) are specified due to erosion concerns (Notes 11, 12, 15). This indicates a known risk of erosion, particularly downstream of the choke valve, which could lead to loss of containment if not adequately monitored and mitigated.</t>
+          <t>The choke valve is a 'step type valve' (Note 16) and on failure, it will remain in its set position. This design choice implies a potential for loss of flow control if the choke fails, relying on upstream (wing valve 13-ESV 2253) or downstream (quick dump valve 13-XY 2253) isolation for intervention.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>XE 2270, NE 2269</t>
+          <t>13-ESV 2253, 13-XY 2253, NOTE 16</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Inadequate isolation / Maintenance hazard</t>
+          <t>Failure to close (ESV), Failure to open (ESV), No emergency shutdown</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Notes 23 and 24 concerning the multiphase meter (13-XJ54) refer to "ISOLATION VALVES FOR FIT BY PIPING DEPARTMENT." This suggests potential uncertainty or reliance on future design for critical isolation, which could lead to inadequate isolation during maintenance or operational issues.</t>
+          <t>Emergency shut-off valves (ESV 2251, ESV 2252, ESV 2253) are critical safety barriers. Their actuation relies on hydraulic power supplied from a Hydraulic Power Unit (HPU). Lack of explicit redundancy or detailed failure modes for the hydraulic supply could compromise the wellhead's emergency shutdown capability.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13-XJ54, FE 2275, DT 2276, TIT 2273, FI 2275A, FI 2275B, FI 2275C, PI 2274</t>
+          <t>13-ESV 2251, 13-ESV 2252, 13-ESV 2253, H013-P-E-001, H013-P-E-008, H013-P-E-013</t>
         </is>
       </c>
     </row>
@@ -620,17 +620,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Hydraulic shock / Too fast operation</t>
+          <t>Erosion, Leak, No detection (of sand)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The "QUICK DUMP VALVE" (XY 2253) is associated with Note 9, which warns about "VALVE OPENING TIME LONG ENOUGH TO AVOID HYDRAULIC SHOCK." This highlights a design consideration for potential hydraulic shock if the valve operates too rapidly, posing a risk to piping integrity.</t>
+          <t>Multiple sand detection instruments (SI 2805, SI 2902, SI 2804, SI 3001) and notes related to sand erosion (Notes 11, 12, 14, 15, 27) highlight a known risk. This indicates a potential for pipe/equipment thinning and possible loss of containment if sand production is not effectively monitored and managed, especially near bends and tees.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>XY 2253</t>
+          <t>SI 2805, SI 2902, SI 2804, SI 3001, 13-XE 2270, NOTE 11, NOTE 12, NOTE 14, NOTE 15, NOTE 27</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -680,160 +680,160 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>XV 2271</t>
+          <t>H042-P-F-006</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>bekreftet ((type, nr)-match)</t>
+          <t>ukjent format / mulig hallusinasjon</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>observation 1: No flow / More flow</t>
+          <t>observation 1: No flow (of chemical), Less flow (of chemical), Maintenance difficulty</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>H042-P-*F-006</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>H042-P-F-004</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>ukjent format / mulig hallusinasjon</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>observation 1: No flow / More flow</t>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>observation 1: No flow (of chemical), Less flow (of chemical), Maintenance difficulty</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>H042-P-*F-004</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>H042-P-F-005</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ukjent format / mulig hallusinasjon</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>observation 1: No flow / More flow</t>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>observation 1: No flow (of chemical), Less flow (of chemical), Maintenance difficulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>H042-P-*F-005</t>
+          <t>42-2000CC</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>ukjent format / mulig hallusinasjon</t>
+          <t>bekreftet i uttrekket</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>observation 1: No flow / More flow</t>
+          <t>observation 1: No flow (of chemical), Less flow (of chemical), Maintenance difficulty</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>ESV 2252</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>observation 2: High differential pressure</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>42-2000CA</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>observation 1: No flow (of chemical), Less flow (of chemical), Maintenance difficulty</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>PDI 2260</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>observation 2: High differential pressure</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>42-2000CG</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>observation 1: No flow (of chemical), Less flow (of chemical), Maintenance difficulty</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>PI 2256A</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>observation 2: High differential pressure</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>13-XJ54</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>PI 2256B</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>observation 2: High differential pressure</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>13-PDI 2260</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>HV 2264</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>observation 3: Wrong position / More flow / No flow</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2277</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>XE 2270</t>
+          <t>13-LL 2277</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -843,303 +843,1714 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>observation 4: Erosion / Leak</t>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>NE 2269</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>observation 4: Erosion / Leak</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>13-PT 2277</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>13-XJ54</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>13-2015PT</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>FE 2275</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>13-2075PT</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>DT 2276</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>13-2077PT</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>TIT 2273</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>13-2076PT</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>FI 2275A</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>13-2126PT</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>FI 2275B</t>
+          <t>NOTE 15</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>observation 2: More flow (unmeasured), Reverse flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>13-PI 2260</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
           <t>bekreftet ((type, nr)-match)</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>FI 2275C</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>observation 3: High pressure, Low pressure, No isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2256A</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>observation 3: High pressure, Low pressure, No isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2255A</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>observation 3: High pressure, Low pressure, No isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2254A</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>observation 3: High pressure, Low pressure, No isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2256B</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>observation 3: High pressure, Low pressure, No isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2255B</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>observation 3: High pressure, Low pressure, No isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2254B</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>observation 3: High pressure, Low pressure, No isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>NOTE 31</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>observation 3: High pressure, Low pressure, No isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>13-ESV 2253</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>observation 4: No flow, More flow, Less control</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>13-XY 2253</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>observation 4: No flow, More flow, Less control</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>NOTE 16</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>observation 4: No flow, More flow, Less control</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>13-ESV 2251</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>observation 5: Failure to close (ESV), Failure to open (ESV), No emergency shutdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>13-ESV 2252</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>observation 5: Failure to close (ESV), Failure to open (ESV), No emergency shutdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>13-ESV 2253</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>observation 5: Failure to close (ESV), Failure to open (ESV), No emergency shutdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>H013-P-E-001</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>observation 5: Failure to close (ESV), Failure to open (ESV), No emergency shutdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>H013-P-E-008</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>observation 5: Failure to close (ESV), Failure to open (ESV), No emergency shutdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>H013-P-E-013</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>observation 5: Failure to close (ESV), Failure to open (ESV), No emergency shutdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>SI 2805</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>observation 6: Erosion, Leak, No detection (of sand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>SI 2902</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>observation 6: Erosion, Leak, No detection (of sand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>SI 2804</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>observation 6: Erosion, Leak, No detection (of sand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>SI 3001</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>observation 6: Erosion, Leak, No detection (of sand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>13-XE 2270</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>observation 6: Erosion, Leak, No detection (of sand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>NOTE 11</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Erosion, Leak, No detection (of sand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>NOTE 12</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Erosion, Leak, No detection (of sand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>NOTE 14</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Erosion, Leak, No detection (of sand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>NOTE 15</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Erosion, Leak, No detection (of sand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>NOTE 27</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Erosion, Leak, No detection (of sand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>13-XV 2271</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Actuated block valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>13-ZS 2272 L</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>bekreftet ((type, nr)-match)</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>PI 2274</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Level switch, low (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>13-ZL 2271 H</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>bekreftet ((type, nr)-match)</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>observation 5: Inadequate isolation / Maintenance hazard</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>XY 2253</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Level switch, high (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>13-ZL 2272 L</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>bekreftet ((type, nr)-match)</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>observation 6: Hydraulic shock / Too fast operation</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>XV 2271</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Level switch, low (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2260A</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>13-XY 2253</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Actuated valve (Quick dump valve, local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>13-TI 2263</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Temperature indicator (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>13-TT 2263</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Temperature transmitter (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>13-PX 2299</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure transmitter (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>13-PDI 2299</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure differential indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>13-PDI 2260</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure differential indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2262A</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>13-HY 2264B</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Manual valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>13-HY 2264A</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Manual valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>13-PT 2262</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure transmitter (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2277</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>13-LL 2277</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Level indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>13-PT 2277</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure transmitter (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>13-HIC 2264</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Hand indicator controller (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>13-ZI 2264</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Level indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>13-ZS 2264 L</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>bekreftet ((type, nr)-match)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>XY 2253</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Level switch, low (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>13-SI 2805</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Sand indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>13-SI 2902</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Sand indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2282</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure indicator (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2260B</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure indicator (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>13-ESV 2252</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Emergency shut-off valve (master valve)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>13-XY 2252</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Actuated valve (master valve)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>13-ESV 2253</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Emergency shut-off valve (wing valve)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2285</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure indicator (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>13-SI 2701</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Sand indicator (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>13-ZS 2279 L</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>bekreftet ((type, nr)-match)</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: quick dump valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>ESV 2252</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Level switch, low (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>13-ZL 2279 H</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Level switch, high (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>13-XV 2279</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Actuated block valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>13-XY 2279</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Actuated valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>13-XE 2270</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Analyser (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>13-XI 2270</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Indicator (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>13-TI 2273</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Temperature indicator (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>13-FI 2274</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>NY KANDIDAT - sjekk tegning</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: emergency shutoff valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>ESV 2253</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Flow indicator (oil, panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>13-FI 2275A</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Flow indicator (water, panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>13-FI 2275B</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Flow indicator (gas, panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>13-FI 2275C</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Flow indicator (gas, panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>13-NE 2269</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Noise element (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2014</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>13-PDI 2014</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure differential indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>13-ZL 2287 H</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Level switch, high (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>13-ZS 2287 L</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Level switch, low (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>13-HS 2287</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Hand switch (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>13-HV 2287</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Manual valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2286</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure indicator (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>13-TI 2286</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Temperature indicator (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>13-ESV 2251</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Emergency shut-off valve (SSSV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>13-XT 2286</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Transmitter (general, local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>13-PI 2284</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure indicator (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>13-SI 3902</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>NY KANDIDAT - sjekk tegning</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: emergency shutoff valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>HV 2264</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Sand indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>13-SI 3903</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>NY KANDIDAT - sjekk tegning</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: choke valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>XY 2279</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>XV 2279</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet ((type, nr)-match)</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Totals: 1 verified · 13 verified (normalised) · 10 new candidates · 3 unknown format</t>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Sand indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>13-SC 2280</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Safety controller (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>13-TI 2280</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Temperature indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>13-TT 2280</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Temperature transmitter (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>13-SI 3001</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Sand indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>13-SI 2804</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Sand indicator (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>13-DT 2276</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Density transmitter (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>13-FE 2275</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Flow element (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>13-PIT 2274</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure indicating transmitter (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>13-FE 2278</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Flow element (local)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>13-FIT 2278</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Flow indicating transmitter (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>13-TIT 2273</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Temperature indicating transmitter (panel mounted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Totals: 66 verified · 9 verified (normalised) · 21 new candidates · 14 unknown format</t>
         </is>
       </c>
     </row>
